--- a/prepare/names.xlsx
+++ b/prepare/names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026-1H609\prepare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E922E88-C763-45CC-868C-F998C36698D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FACC1D-E9E6-4DD4-8B71-C0FC66169F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="104">
   <si>
     <t>権限</t>
   </si>
@@ -305,9 +305,6 @@
     <t>Group7</t>
   </si>
   <si>
-    <t>Group</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -327,6 +324,15 @@
   </si>
   <si>
     <t>score7</t>
+  </si>
+  <si>
+    <t>attend8</t>
+  </si>
+  <si>
+    <t>Group8</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -808,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -816,15 +822,16 @@
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="25.7109375" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
-    <col min="9" max="20" width="9.140625" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="31" hidden="1" customWidth="1"/>
+    <col min="9" max="20" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,10 +899,16 @@
         <v>92</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -939,8 +952,11 @@
       <c r="V2">
         <v>0</v>
       </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -984,8 +1000,11 @@
       <c r="V3">
         <v>0</v>
       </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1041,8 +1060,11 @@
       <c r="V4">
         <v>0</v>
       </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -1098,8 +1120,11 @@
       <c r="V5">
         <v>0</v>
       </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:25">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -1167,8 +1192,14 @@
       <c r="W6" s="5">
         <v>2</v>
       </c>
+      <c r="X6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1233,8 +1264,17 @@
       <c r="V7" s="5">
         <v>0</v>
       </c>
+      <c r="W7" t="s">
+        <v>94</v>
+      </c>
+      <c r="X7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1302,8 +1342,14 @@
       <c r="W8" s="5">
         <v>3</v>
       </c>
+      <c r="X8" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1373,8 +1419,14 @@
       <c r="W9" s="5">
         <v>1</v>
       </c>
+      <c r="X9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:25">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1442,8 +1494,14 @@
       <c r="W10" s="5">
         <v>3</v>
       </c>
+      <c r="X10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1513,8 +1571,14 @@
       <c r="W11" s="5">
         <v>1</v>
       </c>
+      <c r="X11" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1584,8 +1648,14 @@
       <c r="W12" s="5">
         <v>1</v>
       </c>
+      <c r="X12" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1650,8 +1720,14 @@
       <c r="W13" s="5">
         <v>2</v>
       </c>
+      <c r="X13" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:25">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1716,7 +1792,13 @@
         <v>3</v>
       </c>
       <c r="W14" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="X14" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1767,7 +1849,7 @@
         <v>81</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>82</v>
@@ -1776,7 +1858,7 @@
         <v>85</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>86</v>
@@ -1785,7 +1867,7 @@
         <v>87</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>88</v>
@@ -1794,7 +1876,7 @@
         <v>89</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>90</v>
@@ -1803,7 +1885,7 @@
         <v>91</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>92</v>
@@ -1812,7 +1894,7 @@
         <v>93</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15.75" thickTop="1">
@@ -2121,7 +2203,9 @@
       <c r="AA6" s="5">
         <v>2</v>
       </c>
-      <c r="AB6" s="7"/>
+      <c r="AB6" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="2" t="s">
@@ -2202,7 +2286,12 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
-      <c r="AB7" s="7"/>
+      <c r="AA7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="2" t="s">
@@ -2286,7 +2375,9 @@
       <c r="AA8" s="5">
         <v>3</v>
       </c>
-      <c r="AB8" s="7"/>
+      <c r="AB8" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="2" t="s">
@@ -2370,7 +2461,9 @@
       <c r="AA9" s="5">
         <v>1</v>
       </c>
-      <c r="AB9" s="7"/>
+      <c r="AB9" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="2" t="s">
@@ -2454,7 +2547,9 @@
       <c r="AA10" s="5">
         <v>3</v>
       </c>
-      <c r="AB10" s="7"/>
+      <c r="AB10" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="2" t="s">
@@ -2538,7 +2633,9 @@
       <c r="AA11" s="5">
         <v>1</v>
       </c>
-      <c r="AB11" s="7"/>
+      <c r="AB11" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="2" t="s">
@@ -2622,7 +2719,9 @@
       <c r="AA12" s="5">
         <v>1</v>
       </c>
-      <c r="AB12" s="7"/>
+      <c r="AB12" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="2" t="s">
@@ -2703,7 +2802,9 @@
       <c r="AA13" s="5">
         <v>2</v>
       </c>
-      <c r="AB13" s="7"/>
+      <c r="AB13" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="2" t="s">
@@ -2782,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="AA14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB14" s="7">
         <v>3</v>
